--- a/artfynd/A 57150-2023 artfynd.xlsx
+++ b/artfynd/A 57150-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125769209</v>
       </c>
       <c r="B2" t="n">
-        <v>58019</v>
+        <v>58020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 57150-2023 artfynd.xlsx
+++ b/artfynd/A 57150-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125769209</v>
       </c>
       <c r="B2" t="n">
-        <v>58020</v>
+        <v>58021</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>125769218</v>
       </c>
       <c r="B3" t="n">
-        <v>57781</v>
+        <v>57782</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 57150-2023 artfynd.xlsx
+++ b/artfynd/A 57150-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125769209</v>
       </c>
       <c r="B2" t="n">
-        <v>58021</v>
+        <v>58025</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>125769218</v>
       </c>
       <c r="B3" t="n">
-        <v>57782</v>
+        <v>57786</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 57150-2023 artfynd.xlsx
+++ b/artfynd/A 57150-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -907,6 +907,115 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>127700168</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57582</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100001</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Duvhök</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Astur gentilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Köckenmödden, Ramnared, Drängsered, Hl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>371065</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6318456</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hylte</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Drängsered</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jens Ramnebro</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jens Ramnebro</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 57150-2023 artfynd.xlsx
+++ b/artfynd/A 57150-2023 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>127700168</v>
       </c>
       <c r="B4" t="n">
-        <v>57582</v>
+        <v>57584</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 57150-2023 artfynd.xlsx
+++ b/artfynd/A 57150-2023 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>127700168</v>
       </c>
       <c r="B4" t="n">
-        <v>57584</v>
+        <v>57587</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 57150-2023 artfynd.xlsx
+++ b/artfynd/A 57150-2023 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>127700168</v>
       </c>
       <c r="B4" t="n">
-        <v>57587</v>
+        <v>57593</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 57150-2023 artfynd.xlsx
+++ b/artfynd/A 57150-2023 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>127700168</v>
       </c>
       <c r="B4" t="n">
-        <v>57593</v>
+        <v>57594</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 57150-2023 artfynd.xlsx
+++ b/artfynd/A 57150-2023 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>127700168</v>
       </c>
       <c r="B4" t="n">
-        <v>57594</v>
+        <v>57605</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 57150-2023 artfynd.xlsx
+++ b/artfynd/A 57150-2023 artfynd.xlsx
@@ -801,7 +801,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">

--- a/artfynd/A 57150-2023 artfynd.xlsx
+++ b/artfynd/A 57150-2023 artfynd.xlsx
@@ -675,27 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125769209</v>
+        <v>127700168</v>
       </c>
       <c r="B2" t="n">
-        <v>58025</v>
+        <v>57874</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>100001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,13 +708,13 @@
           <t>2</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -752,22 +752,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>08:30</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>09:40</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,42 +784,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125769218</v>
+        <v>125769209</v>
       </c>
       <c r="B3" t="n">
-        <v>57786</v>
+        <v>58327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205976</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -909,44 +903,40 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127700168</v>
+        <v>125769218</v>
       </c>
       <c r="B4" t="n">
-        <v>57605</v>
+        <v>58085</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100001</v>
+        <v>205976</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>1K</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -986,12 +976,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 57150-2023 artfynd.xlsx
+++ b/artfynd/A 57150-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127700168</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125769209</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1015,8 +1030,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125769218</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>